--- a/examples/metrics.xlsx
+++ b/examples/metrics.xlsx
@@ -8,19 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engit-my.sharepoint.com/personal/matteo_zana_eng_it/Documents/Documenti/Engineering/Programmazione/System/Excel-CSV-Converter/examples/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="11_2B59D2BFD38054ED109BBDF3543088B35299F195" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1C4E610F-7568-4C48-AF1A-E0A8A2569138}"/>
+  <xr:revisionPtr revIDLastSave="15" documentId="11_2B59D2BFD38054ED109BBDF3543088B35299F195" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{91B9441D-4BDE-4DE6-ABED-69E88CB36968}"/>
   <bookViews>
-    <workbookView xWindow="37320" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="37320" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="6">
   <si>
     <t>Metric</t>
   </si>
@@ -114,6 +115,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -439,4 +444,30 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29243181-DDCF-4460-B8F6-0C83F4471590}">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2">
+        <v>0.8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>